--- a/radioaparat_linkovi.xlsx
+++ b/radioaparat_linkovi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m1l0s/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m1l0s/Library/Mobile Documents/com~apple~CloudDocs/Apple/iOS apps/radioAPARAT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D32CA3A-D2D4-3741-B53A-A7D7F0179B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475AB8BD-A8D4-F545-A62A-903FBECA59A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16880" xr2:uid="{6FF80182-A761-2647-9A5D-CE1327C51E42}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="235">
   <si>
     <t>ID</t>
   </si>
@@ -495,10 +495,6 @@
   </si>
   <si>
     <t>subotom od 12 do 14h</t>
-  </si>
-  <si>
-    <t>Zato što pesme ponekad spašavaju živote. Zato što od ponuđenog uvek možete da izaberete nešto za sebe. Zato što ispred ukusa mase uvek stoji ukus pojedinca. Super meni je zvanična top-lista Radio Aparata.
-Uređuje i vodi: Svetlana Đolović</t>
   </si>
   <si>
     <t>https://www.facebook.com/supermeniRAj/</t>
@@ -762,6 +758,34 @@
 Snimanje ove emisije omogućeno je uz finansijsku podršku Evropske unije upravljanju migracijama u Srbiji i promovisanju integracije izbeglica i migranata, koje sprovodi Međunarodna organizacija za migracije u partnerstvu sa UNHCR i KIRS.
 Autor emisije je iskljucivo odgovoran za sadržaj, koji nužno ne odražava stavove EU.
 Izvršna produkcija: Radio Aparat i Info park.</t>
+  </si>
+  <si>
+    <t>Zato što pesme ponekad spašavaju živote. Zato što od ponuđenog uvek možete da izaberete nešto za sebe. Zato što ispred ukusa mase uvek stoji ukus pojedinca. Super meni je zvanična top-lista Radio Aparata.
+Uređuje i vodi: Svetlana Đolović</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/super-meni-radio-aparat.png</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/after-hours-radio-aparat-1-1200x1800.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/03/arcadia-radio-aparat.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/gistro-fm-radio-aparat.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/disko-buvljak-radio-aparat-1.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/piratski-satelit-radio-aparat.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/pop-depresija-radio-aparat-1200x1199.png</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/Preslicavanje-radio-aparat.jpg</t>
   </si>
 </sst>
 </file>
@@ -814,7 +838,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -824,7 +848,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1157,6 +1180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC0F6B4F-BD8C-3745-9181-6C92BF1467A2}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1164,50 +1188,50 @@
     <col min="2" max="2" width="25.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.33203125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="27.33203125" style="6" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
     <col min="7" max="12" width="12.83203125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="5" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="5" t="s">
-        <v>161</v>
+      <c r="M1" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1223,8 +1247,11 @@
       <c r="D2" t="s">
         <v>120</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>122</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1240,8 +1267,11 @@
       <c r="D3" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>140</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>126</v>
@@ -1250,7 +1280,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1274,8 +1304,11 @@
       <c r="D5" t="s">
         <v>127</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>128</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1289,10 +1322,10 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1308,11 +1341,11 @@
       <c r="D7" t="s">
         <v>137</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1334,22 +1367,22 @@
         <v>11</v>
       </c>
       <c r="D9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="H9" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="K9" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>158</v>
-      </c>
       <c r="M9" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1365,17 +1398,20 @@
       <c r="D10" t="s">
         <v>148</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:13" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -1397,16 +1433,16 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
+        <v>210</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="J12" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="K12" s="4" t="s">
         <v>212</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1422,7 +1458,7 @@
       <c r="D13" t="s">
         <v>129</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="6" t="s">
         <v>130</v>
       </c>
       <c r="I13" s="4" t="s">
@@ -1442,14 +1478,17 @@
       <c r="D14" t="s">
         <v>132</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="6" t="s">
         <v>142</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>230</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -1460,7 +1499,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>48</v>
       </c>
@@ -1484,14 +1523,14 @@
       <c r="D17" t="s">
         <v>134</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="6" t="s">
         <v>135</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>52</v>
       </c>
@@ -1502,7 +1541,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>53</v>
       </c>
@@ -1524,13 +1563,13 @@
         <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>207</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>206</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>56</v>
       </c>
@@ -1541,7 +1580,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -1563,13 +1602,13 @@
         <v>11</v>
       </c>
       <c r="D23" t="s">
+        <v>214</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>62</v>
       </c>
@@ -1591,10 +1630,10 @@
         <v>11</v>
       </c>
       <c r="D25" t="s">
+        <v>217</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1608,10 +1647,10 @@
         <v>11</v>
       </c>
       <c r="D26" t="s">
+        <v>219</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1627,8 +1666,11 @@
       <c r="D27" t="s">
         <v>138</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="6" t="s">
         <v>139</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>232</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>143</v>
@@ -1653,8 +1695,11 @@
       <c r="D28" t="s">
         <v>146</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="6" t="s">
         <v>147</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1668,10 +1713,13 @@
         <v>11</v>
       </c>
       <c r="D29" t="s">
+        <v>221</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="E29" s="7" t="s">
-        <v>223</v>
+      <c r="F29" s="3" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1685,19 +1733,19 @@
         <v>11</v>
       </c>
       <c r="D30" t="s">
+        <v>151</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="K30" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="L30" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="K30" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>76</v>
       </c>
@@ -1719,10 +1767,10 @@
         <v>20</v>
       </c>
       <c r="D32" t="s">
+        <v>178</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1736,13 +1784,13 @@
         <v>20</v>
       </c>
       <c r="D33" t="s">
+        <v>166</v>
+      </c>
+      <c r="E33" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="E33" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>19</v>
       </c>
@@ -1764,19 +1812,19 @@
         <v>20</v>
       </c>
       <c r="D35" t="s">
+        <v>168</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="H35" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="J35" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="K35" s="4" t="s">
         <v>171</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1790,13 +1838,13 @@
         <v>20</v>
       </c>
       <c r="D36" t="s">
+        <v>223</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="E36" s="7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -1818,22 +1866,22 @@
         <v>20</v>
       </c>
       <c r="D38" t="s">
+        <v>173</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="H38" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="K38" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="H38" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="K38" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -1844,7 +1892,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>87</v>
       </c>
@@ -1855,7 +1903,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>89</v>
       </c>
@@ -1865,8 +1913,8 @@
       <c r="C41" t="s">
         <v>24</v>
       </c>
-      <c r="E41" s="7" t="s">
-        <v>226</v>
+      <c r="E41" s="6" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1880,13 +1928,13 @@
         <v>24</v>
       </c>
       <c r="D42" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="E42" s="7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>93</v>
       </c>
@@ -1896,11 +1944,11 @@
       <c r="C43" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="K43" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1914,16 +1962,16 @@
         <v>24</v>
       </c>
       <c r="D44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E44" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="H44" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="L44" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="L44" s="4" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1937,10 +1985,10 @@
         <v>24</v>
       </c>
       <c r="D45" t="s">
+        <v>184</v>
+      </c>
+      <c r="E45" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1954,16 +2002,16 @@
         <v>24</v>
       </c>
       <c r="D46" t="s">
+        <v>186</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="J46" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="J46" s="4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>100</v>
       </c>
@@ -1973,20 +2021,20 @@
       <c r="C47" t="s">
         <v>24</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="E47" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="K47" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="H47" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>23</v>
       </c>
@@ -1997,7 +2045,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>103</v>
       </c>
@@ -2019,10 +2067,10 @@
         <v>107</v>
       </c>
       <c r="D50" t="s">
+        <v>193</v>
+      </c>
+      <c r="E50" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2036,10 +2084,10 @@
         <v>107</v>
       </c>
       <c r="D51" t="s">
+        <v>195</v>
+      </c>
+      <c r="E51" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2053,13 +2101,13 @@
         <v>107</v>
       </c>
       <c r="D52" t="s">
+        <v>197</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="E52" s="7" t="s">
+      <c r="K52" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2073,10 +2121,10 @@
         <v>107</v>
       </c>
       <c r="D53" t="s">
+        <v>200</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2090,10 +2138,10 @@
         <v>107</v>
       </c>
       <c r="D54" t="s">
+        <v>202</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2107,10 +2155,10 @@
         <v>107</v>
       </c>
       <c r="D55" t="s">
+        <v>204</v>
+      </c>
+      <c r="E55" s="6" t="s">
         <v>205</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2124,13 +2172,13 @@
         <v>107</v>
       </c>
       <c r="D56" t="s">
+        <v>206</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="E56" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:11" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>118</v>
       </c>
@@ -2142,7 +2190,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M57" xr:uid="{CC0F6B4F-BD8C-3745-9181-6C92BF1467A2}"/>
+  <autoFilter ref="A1:M57" xr:uid="{CC0F6B4F-BD8C-3745-9181-6C92BF1467A2}">
+    <filterColumn colId="3">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
@@ -2184,6 +2238,14 @@
     <hyperlink ref="K52" r:id="rId30" xr:uid="{813DE0C0-85CD-BA47-B68B-877E87F51172}"/>
     <hyperlink ref="K12" r:id="rId31" xr:uid="{5A29ECBD-AE3C-5846-B6F0-DD8E6B1E5A45}"/>
     <hyperlink ref="J12" r:id="rId32" xr:uid="{C0E6FF73-51AE-BB41-A58A-4565304510AF}"/>
+    <hyperlink ref="F10" r:id="rId33" xr:uid="{07727EE8-600C-7641-9CA4-3DE0921B3402}"/>
+    <hyperlink ref="F2" r:id="rId34" xr:uid="{E751BE1E-91FA-4F4C-BD7B-1A2568FC1B71}"/>
+    <hyperlink ref="F3" r:id="rId35" xr:uid="{E86BE147-5ED1-FF47-9440-EC4DDE7E660A}"/>
+    <hyperlink ref="F14" r:id="rId36" xr:uid="{06A4177B-92F9-FE4F-83BF-7B3940DC6755}"/>
+    <hyperlink ref="F5" r:id="rId37" xr:uid="{D23123CA-D8FF-8840-B8EB-8B945DBDB264}"/>
+    <hyperlink ref="F27" r:id="rId38" xr:uid="{D6FDBEA1-7B6C-8B42-8C9E-B7CA7ABAB517}"/>
+    <hyperlink ref="F28" r:id="rId39" xr:uid="{C09773AE-599C-EB45-9BCA-089076AC6614}"/>
+    <hyperlink ref="F29" r:id="rId40" xr:uid="{F0534A1E-B569-654F-82FE-2F90A0010A96}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/radioaparat_linkovi.xlsx
+++ b/radioaparat_linkovi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m1l0s/Library/Mobile Documents/com~apple~CloudDocs/Apple/iOS apps/radioAPARAT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475AB8BD-A8D4-F545-A62A-903FBECA59A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7D7E438-7452-A449-95FF-5B6EEC6F8A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16880" xr2:uid="{6FF80182-A761-2647-9A5D-CE1327C51E42}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="254">
   <si>
     <t>ID</t>
   </si>
@@ -592,10 +592,6 @@
   </si>
   <si>
     <t>utorkom od 18.00 do 20.00</t>
-  </si>
-  <si>
-    <t>Ovim programom knjižara Beopolis proširuje komunikaciju sa publikom, obrađujući teme iz kulture, književnosti, obrazovanja, politike i sporta.
-Emisiju uređuje i vodi: Aleksandar (Kafka) Nikolić, osnivač Beopolisa</t>
   </si>
   <si>
     <t>svakog poslednjeg ponedeljka u mesecu od 17 do 18h</t>
@@ -786,6 +782,68 @@
   </si>
   <si>
     <t>https://radioaparat.rs/h-content/uploads/2022/01/Preslicavanje-radio-aparat.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/podzemlje-radio-aparat.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/mono-radio-aparat.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/03/mansarda-radio-aparat.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/dirizabl-radio-aparat.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/ekspedicija-radio-aparat.png</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/orfejeva-kutija-radio-aparat-1200x762.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/reality-check-radio-aparat.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/beopolis-iz-radio-aparata-radio-aparat-1200x525.jpg</t>
+  </si>
+  <si>
+    <t>Beopolis je kultna beogradska knjižara osnovana krajem 1999. godine, u saradnji sa Domom omladine Begrada. Uprkos izazovima i teškim periodima, knjižara je opstala i danas je mesto koje ima značajnu društvenu i kulturnu ulogu u Beogradu, Srbiji i regionu bivše Jugoslavije. Ključni programi Beopolisa obuhvataju pažljivu selekciju nekomercijalne i komercijalne književnosti, promociju relevantnih naslova iz oblasti humanistike, umetnosti, stripa i regionalne književnosti. Beopolis programski pruža podršku nezavisnim i malim izdavačima, učestvuje u organizovanju književnih promocija, tribina, diskusija, festivala. Prepoznat kao prostor okrenut alternativnom i kritičkom, odnos Beopolisa i zajednice je izrazito interaktivan i zasnovan na uzajamnom poverenju. Beopolis je svojim angažmanom i ponekad čak subverzirvnim stavom prema rigidnim i zatvorenim umetničkim i društvenim politikama i praksama, stvorio generacije angažovanih čitalaca i podsticao otvorene diskusije o važnim društvenim i kulturnim pitanjima kroz promociju umetničkih i svih drugih sloboda.
+Knjižara Beopolis od 2016. godine sarađuje sa RadioAparatom. Emisija „Beopolis iz RadioAparata“ emituje se utorkom od 18 do 20 časova i ovim programom knjižara proširuje komunikaciju sa publikom, obrađujući teme iz kulture, književnosti, obrazovanja, politike i sporta. Ova saradnja omogućava Beopolisu da svoje ideje i stavove komunicira putem savremenih medija, jačajući svoju povezanost sa lokalnom i regionalnom zajednicom.
+Emisiju uređuje i vodi Aleksandar (Kafka) Nikolić, osnivač Beopolisa</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/grad-u-prolazu-radio-aparat-1200x800.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/kamilica-radio-aparat.png</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/03/kultur-kajgana-radio-aparat.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/sceniranje-radio-aparat.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/antroposestvije-radio-aparat.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/Liceulice-FM-radio-aparat.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/Radio-galaksija-radio-aparat.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2025/09/Sizoanaliza-radio-aparat-1200x1200.png</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/Nevergrin-radio-aparat.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/Pop-Kujna-radio-aparat.jpg</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/povratak-lopova-radio-aparat-1200x675.png</t>
   </si>
 </sst>
 </file>
@@ -1180,7 +1238,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC0F6B4F-BD8C-3745-9181-6C92BF1467A2}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1251,7 +1308,7 @@
         <v>122</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1271,7 +1328,7 @@
         <v>140</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>126</v>
@@ -1280,7 +1337,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1308,7 +1365,7 @@
         <v>128</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1322,10 +1379,13 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
+        <v>207</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>209</v>
+      <c r="F6" s="3" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1344,8 +1404,11 @@
       <c r="E7" s="6" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F7" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1372,6 +1435,9 @@
       <c r="E9" s="6" t="s">
         <v>156</v>
       </c>
+      <c r="F9" s="3" t="s">
+        <v>236</v>
+      </c>
       <c r="H9" s="4" t="s">
         <v>159</v>
       </c>
@@ -1399,10 +1465,10 @@
         <v>148</v>
       </c>
       <c r="E10" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>227</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>150</v>
@@ -1411,7 +1477,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -1433,16 +1499,19 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
+        <v>209</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="F12" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="K12" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1461,6 +1530,9 @@
       <c r="E13" s="6" t="s">
         <v>130</v>
       </c>
+      <c r="F13" s="3" t="s">
+        <v>238</v>
+      </c>
       <c r="I13" s="4" t="s">
         <v>131</v>
       </c>
@@ -1482,13 +1554,13 @@
         <v>142</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -1499,7 +1571,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>48</v>
       </c>
@@ -1530,7 +1602,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>52</v>
       </c>
@@ -1541,7 +1613,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>53</v>
       </c>
@@ -1563,13 +1635,13 @@
         <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>56</v>
       </c>
@@ -1580,7 +1652,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -1602,13 +1674,13 @@
         <v>11</v>
       </c>
       <c r="D23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>62</v>
       </c>
@@ -1630,10 +1702,10 @@
         <v>11</v>
       </c>
       <c r="D25" t="s">
+        <v>216</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>217</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1647,10 +1719,13 @@
         <v>11</v>
       </c>
       <c r="D26" t="s">
+        <v>218</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>220</v>
+      <c r="F26" s="3" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1670,7 +1745,7 @@
         <v>139</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>143</v>
@@ -1699,7 +1774,7 @@
         <v>147</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1713,13 +1788,13 @@
         <v>11</v>
       </c>
       <c r="D29" t="s">
+        <v>220</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>222</v>
-      </c>
       <c r="F29" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1738,6 +1813,9 @@
       <c r="E30" s="6" t="s">
         <v>152</v>
       </c>
+      <c r="F30" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="K30" s="4" t="s">
         <v>154</v>
       </c>
@@ -1745,7 +1823,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>76</v>
       </c>
@@ -1770,7 +1848,10 @@
         <v>178</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>179</v>
+        <v>242</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1789,8 +1870,11 @@
       <c r="E33" s="6" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F33" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>19</v>
       </c>
@@ -1817,6 +1901,9 @@
       <c r="E35" s="6" t="s">
         <v>169</v>
       </c>
+      <c r="F35" s="3" t="s">
+        <v>244</v>
+      </c>
       <c r="H35" s="4" t="s">
         <v>170</v>
       </c>
@@ -1838,13 +1925,16 @@
         <v>20</v>
       </c>
       <c r="D36" t="s">
+        <v>222</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F36" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -1871,6 +1961,9 @@
       <c r="E38" s="6" t="s">
         <v>174</v>
       </c>
+      <c r="F38" s="3" t="s">
+        <v>246</v>
+      </c>
       <c r="H38" s="4" t="s">
         <v>177</v>
       </c>
@@ -1881,7 +1974,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -1892,7 +1985,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>87</v>
       </c>
@@ -1903,7 +1996,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>89</v>
       </c>
@@ -1914,7 +2007,7 @@
         <v>24</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1928,13 +2021,16 @@
         <v>24</v>
       </c>
       <c r="D42" t="s">
+        <v>179</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F42" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>93</v>
       </c>
@@ -1945,10 +2041,10 @@
         <v>24</v>
       </c>
       <c r="E43" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="K43" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1967,6 +2063,9 @@
       <c r="E44" s="6" t="s">
         <v>163</v>
       </c>
+      <c r="F44" s="3" t="s">
+        <v>248</v>
+      </c>
       <c r="H44" s="4" t="s">
         <v>164</v>
       </c>
@@ -1985,10 +2084,13 @@
         <v>24</v>
       </c>
       <c r="D45" t="s">
+        <v>183</v>
+      </c>
+      <c r="E45" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="E45" s="6" t="s">
-        <v>185</v>
+      <c r="F45" s="3" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2002,16 +2104,19 @@
         <v>24</v>
       </c>
       <c r="D46" t="s">
+        <v>185</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="F46" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="J46" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="J46" s="4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>100</v>
       </c>
@@ -2022,19 +2127,19 @@
         <v>24</v>
       </c>
       <c r="E47" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="K47" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="H47" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>23</v>
       </c>
@@ -2045,7 +2150,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>103</v>
       </c>
@@ -2067,10 +2172,10 @@
         <v>107</v>
       </c>
       <c r="D50" t="s">
+        <v>192</v>
+      </c>
+      <c r="E50" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2084,10 +2189,13 @@
         <v>107</v>
       </c>
       <c r="D51" t="s">
+        <v>194</v>
+      </c>
+      <c r="E51" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>196</v>
+      <c r="F51" s="3" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2101,13 +2209,16 @@
         <v>107</v>
       </c>
       <c r="D52" t="s">
+        <v>196</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="F52" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="K52" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2121,10 +2232,13 @@
         <v>107</v>
       </c>
       <c r="D53" t="s">
+        <v>199</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="E53" s="6" t="s">
-        <v>201</v>
+      <c r="F53" s="3" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2138,10 +2252,10 @@
         <v>107</v>
       </c>
       <c r="D54" t="s">
+        <v>201</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2155,10 +2269,10 @@
         <v>107</v>
       </c>
       <c r="D55" t="s">
+        <v>203</v>
+      </c>
+      <c r="E55" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2172,13 +2286,13 @@
         <v>107</v>
       </c>
       <c r="D56" t="s">
+        <v>205</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="E56" s="6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>118</v>
       </c>
@@ -2190,13 +2304,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M57" xr:uid="{CC0F6B4F-BD8C-3745-9181-6C92BF1467A2}">
-    <filterColumn colId="3">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M57" xr:uid="{CC0F6B4F-BD8C-3745-9181-6C92BF1467A2}"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
@@ -2246,6 +2354,25 @@
     <hyperlink ref="F27" r:id="rId38" xr:uid="{D6FDBEA1-7B6C-8B42-8C9E-B7CA7ABAB517}"/>
     <hyperlink ref="F28" r:id="rId39" xr:uid="{C09773AE-599C-EB45-9BCA-089076AC6614}"/>
     <hyperlink ref="F29" r:id="rId40" xr:uid="{F0534A1E-B569-654F-82FE-2F90A0010A96}"/>
+    <hyperlink ref="F6" r:id="rId41" xr:uid="{30F7D488-149B-6D49-B919-800B2A68C852}"/>
+    <hyperlink ref="F7" r:id="rId42" xr:uid="{B0F0E3C0-8526-0740-B889-6BF3422E60D3}"/>
+    <hyperlink ref="F9" r:id="rId43" xr:uid="{970E7787-AD1F-2B4D-B08C-B58ACF970A3E}"/>
+    <hyperlink ref="F12" r:id="rId44" xr:uid="{24441B47-EA18-E04D-B8EF-CA177C9A9AC4}"/>
+    <hyperlink ref="F13" r:id="rId45" xr:uid="{781FE32F-D880-C64D-A04E-D7A460986DCD}"/>
+    <hyperlink ref="F26" r:id="rId46" xr:uid="{193D7892-2EEF-6141-97F2-3D708C3D2CC1}"/>
+    <hyperlink ref="F30" r:id="rId47" xr:uid="{09797570-22FA-A141-BD6D-10F41D09BB0D}"/>
+    <hyperlink ref="F32" r:id="rId48" xr:uid="{F0934C9E-58EE-FF4B-B8A9-786637D5EEBE}"/>
+    <hyperlink ref="F33" r:id="rId49" xr:uid="{CA91CB82-3F3D-FF45-A67F-6454E70D288C}"/>
+    <hyperlink ref="F35" r:id="rId50" xr:uid="{6A3BE2F8-D9B0-D542-9F53-79DB2B7BD564}"/>
+    <hyperlink ref="F36" r:id="rId51" xr:uid="{90778B8B-230E-3C4E-BB69-AB5EF45FC911}"/>
+    <hyperlink ref="F38" r:id="rId52" xr:uid="{1BA9A77C-4A85-F24E-8AF9-B50B5AFB6E33}"/>
+    <hyperlink ref="F42" r:id="rId53" xr:uid="{FEB38D6B-D4E6-7B45-99E8-4E3C90DB13B2}"/>
+    <hyperlink ref="F44" r:id="rId54" xr:uid="{33DB0183-6916-324A-AD18-7C1452F8C73C}"/>
+    <hyperlink ref="F45" r:id="rId55" xr:uid="{26B7D58B-9311-0C4B-B099-7065EDCA4718}"/>
+    <hyperlink ref="F46" r:id="rId56" xr:uid="{EE61F8FE-7073-FE4D-8099-1E981028660D}"/>
+    <hyperlink ref="F51" r:id="rId57" xr:uid="{E44A0830-EE46-AF4E-8BB7-2EF2807ABD62}"/>
+    <hyperlink ref="F52" r:id="rId58" xr:uid="{58FC44C0-BBDF-D144-B565-0B23179055B8}"/>
+    <hyperlink ref="F53" r:id="rId59" xr:uid="{944162AC-BD30-0E4F-9B64-E4E37111A29A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/radioaparat_linkovi.xlsx
+++ b/radioaparat_linkovi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m1l0s/Library/Mobile Documents/com~apple~CloudDocs/Apple/iOS apps/radioAPARAT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7D7E438-7452-A449-95FF-5B6EEC6F8A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4947A9-F1D5-8C4A-AE28-C44F9E5E3BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16880" xr2:uid="{6FF80182-A761-2647-9A5D-CE1327C51E42}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="257">
   <si>
     <t>ID</t>
   </si>
@@ -844,6 +844,15 @@
   </si>
   <si>
     <t>https://radioaparat.rs/h-content/uploads/2022/01/povratak-lopova-radio-aparat-1200x675.png</t>
+  </si>
+  <si>
+    <t>https://thumbnailer.mixcloud.com/unsafe/272x272/profile/9/d/c/5/3c4e-3ddf-48ec-8034-1ffc948e5f86</t>
+  </si>
+  <si>
+    <t>https://thumbnailer.mixcloud.com/unsafe/272x272/profile/e/3/f/5/9f57-2f86-4281-9bb4-0e8cedf3782c.jpg</t>
+  </si>
+  <si>
+    <t>https://thumbnailer.mixcloud.com/unsafe/272x272/profile/c/0/c/a/7240-9d16-4534-b6d3-43e094edfd1b</t>
   </si>
 </sst>
 </file>
@@ -1598,6 +1607,9 @@
       <c r="E17" s="6" t="s">
         <v>135</v>
       </c>
+      <c r="F17" s="3" t="s">
+        <v>254</v>
+      </c>
       <c r="H17" s="4" t="s">
         <v>136</v>
       </c>
@@ -2257,6 +2269,9 @@
       <c r="E54" s="6" t="s">
         <v>202</v>
       </c>
+      <c r="F54" s="3" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="55" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
@@ -2290,6 +2305,9 @@
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2373,6 +2391,9 @@
     <hyperlink ref="F51" r:id="rId57" xr:uid="{E44A0830-EE46-AF4E-8BB7-2EF2807ABD62}"/>
     <hyperlink ref="F52" r:id="rId58" xr:uid="{58FC44C0-BBDF-D144-B565-0B23179055B8}"/>
     <hyperlink ref="F53" r:id="rId59" xr:uid="{944162AC-BD30-0E4F-9B64-E4E37111A29A}"/>
+    <hyperlink ref="F17" r:id="rId60" xr:uid="{35940410-BC23-AC4B-A7AF-C89A745648CA}"/>
+    <hyperlink ref="F54" r:id="rId61" xr:uid="{C4BEFDE5-6D1F-3842-A4ED-8CE7D5A429B1}"/>
+    <hyperlink ref="F56" r:id="rId62" xr:uid="{061E23FF-74A9-484F-8DEC-0693638A5736}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/radioaparat_linkovi.xlsx
+++ b/radioaparat_linkovi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m1l0s/Library/Mobile Documents/com~apple~CloudDocs/Apple/iOS apps/radioAPARAT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4947A9-F1D5-8C4A-AE28-C44F9E5E3BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA25A4CD-A208-CC44-B948-6A5DC1027AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16880" xr2:uid="{6FF80182-A761-2647-9A5D-CE1327C51E42}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="OPŠTI LINKOVI" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMISIJE!$A$1:$M$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMISIJE!$A$1:$N$57</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="258">
   <si>
     <t>ID</t>
   </si>
@@ -637,9 +637,6 @@
   </si>
   <si>
     <t>https://www.mixcloud.com/U_raljama_osećanja/</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> svake prve nedelje u mesecu od 12 do 15h</t>
   </si>
   <si>
     <t>Presek aktuelne filmske i televizijske produkcije od striminga do bioskopa i nazad.
@@ -853,6 +850,12 @@
   </si>
   <si>
     <t>https://thumbnailer.mixcloud.com/unsafe/272x272/profile/c/0/c/a/7240-9d16-4534-b6d3-43e094edfd1b</t>
+  </si>
+  <si>
+    <t>CHECK</t>
+  </si>
+  <si>
+    <t>svake prve nedelje u mesecu od 12 do 15h</t>
   </si>
 </sst>
 </file>
@@ -905,13 +908,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -920,6 +922,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1245,21 +1256,43 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{AE51EA06-A6B9-FA47-85F2-F901F4ACCB60}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="Office.AutoShowTaskpaneWithDocument" value="true"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC0F6B4F-BD8C-3745-9181-6C92BF1467A2}">
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.33203125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="12" width="12.83203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="27.33203125" style="5" customWidth="1"/>
+    <col min="6" max="12" width="12.83203125" style="2" customWidth="1"/>
+    <col min="13" max="14" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1272,35 +1305,38 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="6" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N1" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1313,14 +1349,18 @@
       <c r="D2" t="s">
         <v>120</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>122</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>226</v>
+      </c>
+      <c r="N2" s="7" t="str">
+        <f>IF((COUNTA(A2,B2,C2,E2,F2))=5,"OK","NOT OK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1333,20 +1373,24 @@
       <c r="D3" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>140</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="I3" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N3" s="7" t="str">
+        <f t="shared" ref="N3:N57" si="0">IF((COUNTA(A3,B3,C3,E3,F3))=5,"OK","NOT OK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1356,8 +1400,12 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N4" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1370,14 +1418,18 @@
       <c r="D5" t="s">
         <v>127</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>128</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>229</v>
+      </c>
+      <c r="N5" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1388,16 +1440,20 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>208</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>233</v>
+      </c>
+      <c r="N6" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1410,14 +1466,18 @@
       <c r="D7" t="s">
         <v>137</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>141</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>234</v>
+      </c>
+      <c r="N7" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1427,8 +1487,12 @@
       <c r="C8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N8" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1441,26 +1505,30 @@
       <c r="D9" t="s">
         <v>155</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>156</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="H9" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>157</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N9" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1473,20 +1541,24 @@
       <c r="D10" t="s">
         <v>148</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N10" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -1496,8 +1568,12 @@
       <c r="C11" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N11" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -1508,22 +1584,26 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
+        <v>208</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="F12" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N12" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -1536,17 +1616,21 @@
       <c r="D13" t="s">
         <v>129</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>130</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="I13" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N13" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -1559,17 +1643,21 @@
       <c r="D14" t="s">
         <v>132</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>142</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K14" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N14" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -1579,8 +1667,12 @@
       <c r="C15" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N15" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>48</v>
       </c>
@@ -1590,8 +1682,12 @@
       <c r="C16" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N16" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -1604,17 +1700,21 @@
       <c r="D17" t="s">
         <v>134</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>135</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H17" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N17" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>52</v>
       </c>
@@ -1624,8 +1724,12 @@
       <c r="C18" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N18" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>53</v>
       </c>
@@ -1635,8 +1739,12 @@
       <c r="C19" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N19" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -1647,13 +1755,17 @@
         <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>205</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>204</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="N20" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>56</v>
       </c>
@@ -1663,8 +1775,12 @@
       <c r="C21" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N21" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -1674,8 +1790,12 @@
       <c r="C22" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N22" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -1686,13 +1806,17 @@
         <v>11</v>
       </c>
       <c r="D23" t="s">
+        <v>212</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N23" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>62</v>
       </c>
@@ -1702,8 +1826,12 @@
       <c r="C24" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N24" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>64</v>
       </c>
@@ -1714,13 +1842,17 @@
         <v>11</v>
       </c>
       <c r="D25" t="s">
+        <v>215</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N25" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>66</v>
       </c>
@@ -1731,16 +1863,20 @@
         <v>11</v>
       </c>
       <c r="D26" t="s">
+        <v>217</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>219</v>
-      </c>
       <c r="F26" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>238</v>
+      </c>
+      <c r="N26" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>68</v>
       </c>
@@ -1753,23 +1889,27 @@
       <c r="D27" t="s">
         <v>138</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="5" t="s">
         <v>139</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="H27" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="J27" s="4" t="s">
+      <c r="J27" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="K27" s="4" t="s">
+      <c r="K27" s="3" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N27" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>69</v>
       </c>
@@ -1782,14 +1922,18 @@
       <c r="D28" t="s">
         <v>146</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="5" t="s">
         <v>147</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>231</v>
+      </c>
+      <c r="N28" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>72</v>
       </c>
@@ -1800,16 +1944,20 @@
         <v>11</v>
       </c>
       <c r="D29" t="s">
+        <v>219</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>221</v>
-      </c>
       <c r="F29" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>232</v>
+      </c>
+      <c r="N29" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>73</v>
       </c>
@@ -1822,20 +1970,24 @@
       <c r="D30" t="s">
         <v>151</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="5" t="s">
         <v>152</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="K30" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="L30" s="4" t="s">
+      <c r="L30" s="3" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N30" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>76</v>
       </c>
@@ -1845,8 +1997,12 @@
       <c r="C31" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N31" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>79</v>
       </c>
@@ -1859,14 +2015,18 @@
       <c r="D32" t="s">
         <v>178</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>242</v>
+      <c r="E32" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+      <c r="N32" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>22</v>
       </c>
@@ -1879,14 +2039,18 @@
       <c r="D33" t="s">
         <v>166</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="5" t="s">
         <v>167</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>242</v>
+      </c>
+      <c r="N33" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>19</v>
       </c>
@@ -1896,8 +2060,12 @@
       <c r="C34" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N34" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>83</v>
       </c>
@@ -1910,23 +2078,27 @@
       <c r="D35" t="s">
         <v>168</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="5" t="s">
         <v>169</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="H35" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="J35" s="4" t="s">
+      <c r="J35" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="K35" s="4" t="s">
+      <c r="K35" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N35" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>84</v>
       </c>
@@ -1937,16 +2109,20 @@
         <v>20</v>
       </c>
       <c r="D36" t="s">
+        <v>221</v>
+      </c>
+      <c r="E36" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>223</v>
-      </c>
       <c r="F36" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>244</v>
+      </c>
+      <c r="N36" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -1956,8 +2132,12 @@
       <c r="C37" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N37" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -1970,23 +2150,27 @@
       <c r="D38" t="s">
         <v>173</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E38" s="5" t="s">
         <v>174</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="H38" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="J38" s="4" t="s">
+      <c r="J38" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="K38" s="4" t="s">
+      <c r="K38" s="3" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N38" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -1996,8 +2180,12 @@
       <c r="C39" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N39" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>87</v>
       </c>
@@ -2007,8 +2195,12 @@
       <c r="C40" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N40" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>89</v>
       </c>
@@ -2018,11 +2210,15 @@
       <c r="C41" t="s">
         <v>24</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E41" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="N41" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>91</v>
       </c>
@@ -2035,14 +2231,18 @@
       <c r="D42" t="s">
         <v>179</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="5" t="s">
         <v>180</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>246</v>
+      </c>
+      <c r="N42" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>93</v>
       </c>
@@ -2052,14 +2252,18 @@
       <c r="C43" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="K43" s="4" t="s">
+      <c r="K43" s="3" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N43" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>94</v>
       </c>
@@ -2072,20 +2276,24 @@
       <c r="D44" t="s">
         <v>162</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="5" t="s">
         <v>163</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="H44" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="L44" s="4" t="s">
+      <c r="L44" s="3" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N44" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>97</v>
       </c>
@@ -2098,14 +2306,18 @@
       <c r="D45" t="s">
         <v>183</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="5" t="s">
         <v>184</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>248</v>
+      </c>
+      <c r="N45" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>98</v>
       </c>
@@ -2118,17 +2330,21 @@
       <c r="D46" t="s">
         <v>185</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="5" t="s">
         <v>186</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="J46" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="J46" s="3" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N46" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>100</v>
       </c>
@@ -2138,20 +2354,24 @@
       <c r="C47" t="s">
         <v>24</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="H47" s="4" t="s">
+      <c r="H47" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="J47" s="4" t="s">
+      <c r="J47" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="K47" s="4" t="s">
+      <c r="K47" s="3" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N47" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>23</v>
       </c>
@@ -2161,8 +2381,12 @@
       <c r="C48" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N48" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>103</v>
       </c>
@@ -2172,8 +2396,12 @@
       <c r="C49" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N49" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>105</v>
       </c>
@@ -2184,13 +2412,17 @@
         <v>107</v>
       </c>
       <c r="D50" t="s">
+        <v>257</v>
+      </c>
+      <c r="E50" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="E50" s="6" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N50" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>108</v>
       </c>
@@ -2201,16 +2433,20 @@
         <v>107</v>
       </c>
       <c r="D51" t="s">
+        <v>193</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>195</v>
-      </c>
       <c r="F51" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>250</v>
+      </c>
+      <c r="N51" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>109</v>
       </c>
@@ -2221,19 +2457,23 @@
         <v>107</v>
       </c>
       <c r="D52" t="s">
+        <v>195</v>
+      </c>
+      <c r="E52" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="F52" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="K52" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N52" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>111</v>
       </c>
@@ -2244,16 +2484,20 @@
         <v>107</v>
       </c>
       <c r="D53" t="s">
+        <v>198</v>
+      </c>
+      <c r="E53" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="E53" s="6" t="s">
-        <v>200</v>
-      </c>
       <c r="F53" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>252</v>
+      </c>
+      <c r="N53" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>113</v>
       </c>
@@ -2264,16 +2508,20 @@
         <v>107</v>
       </c>
       <c r="D54" t="s">
+        <v>200</v>
+      </c>
+      <c r="E54" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="E54" s="6" t="s">
-        <v>202</v>
-      </c>
       <c r="F54" s="3" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>254</v>
+      </c>
+      <c r="N54" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>115</v>
       </c>
@@ -2284,13 +2532,17 @@
         <v>107</v>
       </c>
       <c r="D55" t="s">
+        <v>202</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="E55" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N55" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>117</v>
       </c>
@@ -2301,16 +2553,20 @@
         <v>107</v>
       </c>
       <c r="D56" t="s">
+        <v>204</v>
+      </c>
+      <c r="E56" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="E56" s="6" t="s">
-        <v>206</v>
-      </c>
       <c r="F56" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>255</v>
+      </c>
+      <c r="N56" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>118</v>
       </c>
@@ -2320,9 +2576,13 @@
       <c r="C57" t="s">
         <v>107</v>
       </c>
+      <c r="N57" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M57" xr:uid="{CC0F6B4F-BD8C-3745-9181-6C92BF1467A2}"/>
+  <autoFilter ref="A1:N57" xr:uid="{CC0F6B4F-BD8C-3745-9181-6C92BF1467A2}"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/radioaparat_linkovi.xlsx
+++ b/radioaparat_linkovi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/m1l0s/Library/Mobile Documents/com~apple~CloudDocs/Apple/iOS apps/radioAPARAT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA25A4CD-A208-CC44-B948-6A5DC1027AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB56CEDD-8BBA-F049-B9F2-295BF468D054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16880" xr2:uid="{6FF80182-A761-2647-9A5D-CE1327C51E42}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="OPŠTI LINKOVI" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMISIJE!$A$1:$N$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMISIJE!$A$1:$O$57</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="315">
   <si>
     <t>ID</t>
   </si>
@@ -856,6 +856,186 @@
   </si>
   <si>
     <t>svake prve nedelje u mesecu od 12 do 15h</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/tegla_rs/</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/diskobuvljak/</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/jovana-nikolic5/</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/Nevergrin/</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/kulturkokoska/</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/popkujna/</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/NightWavesSessions/</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/zelenikacket/</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/Arcadia2017/</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/anadajic/</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/popdepression/</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/nebojsa-krivokuca/</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/radiogalaksija/</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/Antroposestvije/</t>
+  </si>
+  <si>
+    <t>https://www.popdepresija.com</t>
+  </si>
+  <si>
+    <t>https://preslicavanje.blogspot.com</t>
+  </si>
+  <si>
+    <t>ARHIVIRANO</t>
+  </si>
+  <si>
+    <t>DA</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/djacim/</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/reggaefever/</t>
+  </si>
+  <si>
+    <t>https://thumbnailer.mixcloud.com/unsafe/272x272/profile/3/4/7/2/3886-75dd-4dce-8dee-b1b88a21295e</t>
+  </si>
+  <si>
+    <t>svake druge srede od 17 do 18h</t>
+  </si>
+  <si>
+    <t>Radio-emisija iz Novog Sada posvećena istinskom roots, rockers i dub zvuku, originalnim porukama i bass kulturi. Kroz retke i ekskluzivne trake, kao i mnogobrojne goste, emisija ima za cilj ne samo da slušaoce uvede u magiju reggae muzike, već i da ih upozna sa aktuelnostima: novim izvođačima i producentima koji prate roots školu starih majstora.
+Voditelj emisije je dugogodišnji reggae novinar i selektor Nenad Pekez aka Mizizi.</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/reggaefever.radio</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reggaefeverserbia/</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@reggaefeverserbia</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/HoboCan/</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/radio808/</t>
+  </si>
+  <si>
+    <t>nedeljom od 10 do 11h</t>
+  </si>
+  <si>
+    <t>Arheofonija je emisija koja se bavi muzikom od prvih zvučnih zapisa do 1955. godine, postavljajući
+muziku koju obrađuje u socijalni, istorijski ili kulturološki kontekst.
+Arheofonija je u periodu od septembra 2018. do oktobra 2022. godine funkcionisala kao podkast.
+Epizode su postavljane dva puta mesečno i u tom periodu je snimljeno ravno sto epizoda.
+Od nedelje, 5. novembra 2023, na Radio Aparatu možete slušati emisije iz arhive Arheofonije, a jednom mesečno moći ćete da pratite i nove epizode.
+Arheofoniju uređuje i vodi: Ivan Čkonjević</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/arheofonija-radio-aparat-1200x1200.jpg</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/Arheofonija/</t>
+  </si>
+  <si>
+    <t>Balkan World Music Chart je međunarodni panel koji čine world music stručnjaci, novinari, kritičari, promoteri, organizatori manifestacija… Pokrenut je pod okriljem World Music asocijacije Srbije, u proleće 2019. godine, sa idejom šire promocije balkanske muzike i povećanja vidljivosti umetnika i bendova povezanih sa Balkanom. Sam pojam “Muzika Balkana“ je u slučaju panela BWMC doživljen dovoljno široko, tako da obuhvata raznovrsnu tradicionalnu i world muziku, koja ima direktnih ili sasvim udaljenih dodira sa balkanskim nasleđem i koju stvaraju kako umetnici sa Balkana, tako i oni koji žive izvan ovog geografskog prostora, ali neguju elemente muzičkog Balkana u svom izrazu, Rad panela BWMC podrazumeva glasanje i objavljivanje kvartalnih Top 10 listi najboljih novijih albuma i jednu Top 20 godišnju listu najboljih albuma iz prethodne godine.</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/balkan-world-music-chart-radio-aparat-1.png</t>
+  </si>
+  <si>
+    <t>https://worldmusic.org.rs/</t>
+  </si>
+  <si>
+    <t>prve nedelje u mesecu od 20:00 do 22:00</t>
+  </si>
+  <si>
+    <t>Night Waves Sessions je autorska muzička emisija posvećena kros-kulturalnom i svetu world muzike, istraživačka i otkrivalačka emisija koja se temelji na različitostima i na fuziji.
+Uređuje i vodi: Dušan Pavlović</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/Night-Waves-Sessions-radio-aparat-1200x1200.jpg</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/keponi/</t>
+  </si>
+  <si>
+    <t>https://thumbnailer.mixcloud.com/unsafe/272x272/profile/4/d/5/8/8703-ae50-4283-9a59-bdace7ac8f9e.jpg</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/moma954/</t>
+  </si>
+  <si>
+    <t>https://thumbnailer.mixcloud.com/unsafe/272x272/profile/1/c/3/4/92bc-54a7-4f63-b980-c3071575c874.jpeg</t>
+  </si>
+  <si>
+    <t>povremeno petkom od 14 do 16h</t>
+  </si>
+  <si>
+    <t>Priprema: Momčilo Rajin</t>
+  </si>
+  <si>
+    <t>https://thumbnailer.mixcloud.com/unsafe/272x272/profile/d/7/d/3/c816-ebfc-4713-a3d6-c2790f850d32</t>
+  </si>
+  <si>
+    <t>svakog drugog petka od 18 do 19h</t>
+  </si>
+  <si>
+    <t>Zvučna etnografija je radio-emisija koja teži tome da kroz zvučna istraživanja poveže teorijska promišljanja kulture i primere iz svakodnevice. Ona predstavlja polje prožimanja i prelivanja teorijskih koncepata, kulturnih izraza i iskustava različitih društvenih aktera/ki, te teži da široj publici približi socio-kulturne teme kroz galeriju primera iz života i uzbudljive zvučne manifestacije.
+Autorke: Iva Janković i Lara Končar</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/zvucna-etnografija-radio-aparat.png</t>
+  </si>
+  <si>
+    <t>https://www.mixcloud.com/zvucnaetnografija/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/zvucna_etnografija/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/zvucnaetnografija/</t>
+  </si>
+  <si>
+    <t>svake druge nedelje od 18:00 do 20:00</t>
+  </si>
+  <si>
+    <t>Zeleni kačket je primarno obeležje nezvaničnog projekta koji su u avgustu 2018. godine pokrenule Kristina Milosavljević, Anđela Milosavljević, Maša Živković i Varvara Vučković. Iz emisije u emisiju kačket menja svoju funkciju, osobu koju štiti, prestaje da bude kačket i postaje zaštitini znak emisije (teme) u kojoj se nalazi. Zelenim kačketom manipuliše grupa muzičkih, filmskih, književnih, likovnih i pivskih entuzijasta koja raspolaže velikom željom za razmenom dragulja u sferi gorepomenutih tema, ali i šire od toga. Od 2021. smo i na radioAparatu.
+Autorski tim trenutno čine Kristina Milosavljević, Pavle Banjac i Mladen Ilić.</t>
+  </si>
+  <si>
+    <t>https://radioaparat.rs/h-content/uploads/2022/01/Zeleni-Kacket-radio-aparat.jpg</t>
+  </si>
+  <si>
+    <t>https://zelenikacket.rs</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/zelenikacket_drami/</t>
   </si>
 </sst>
 </file>
@@ -908,7 +1088,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -928,9 +1108,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1280,7 +1457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC0F6B4F-BD8C-3745-9181-6C92BF1467A2}">
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.33203125" bestFit="1" customWidth="1"/>
@@ -1289,10 +1466,10 @@
     <col min="4" max="4" width="28.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.33203125" style="5" customWidth="1"/>
     <col min="6" max="12" width="12.83203125" style="2" customWidth="1"/>
-    <col min="13" max="14" width="10.83203125" style="2"/>
+    <col min="13" max="15" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1335,8 +1512,11 @@
       <c r="N1" s="6" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O1" s="6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1355,12 +1535,16 @@
       <c r="F2" s="3" t="s">
         <v>226</v>
       </c>
+      <c r="H2" s="3" t="s">
+        <v>277</v>
+      </c>
       <c r="N2" s="7" t="str">
-        <f>IF((COUNTA(A2,B2,C2,E2,F2))=5,"OK","NOT OK")</f>
+        <f>IF((COUNTA(A2,B2,C2,D2,E2,F2,H2))=7,"OK","NOT OK")</f>
         <v>OK</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O2" s="7"/>
+    </row>
+    <row r="3" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1379,6 +1563,9 @@
       <c r="F3" s="3" t="s">
         <v>227</v>
       </c>
+      <c r="H3" s="3" t="s">
+        <v>266</v>
+      </c>
       <c r="I3" s="3" t="s">
         <v>126</v>
       </c>
@@ -1386,11 +1573,14 @@
         <v>124</v>
       </c>
       <c r="N3" s="7" t="str">
-        <f t="shared" ref="N3:N57" si="0">IF((COUNTA(A3,B3,C3,E3,F3))=5,"OK","NOT OK")</f>
+        <f t="shared" ref="N3:N57" si="0">IF((COUNTA(A3,B3,C3,D3,E3,F3,H3))=7,"OK","NOT OK")</f>
         <v>OK</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O3" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1400,12 +1590,27 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
+      <c r="D4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>290</v>
+      </c>
       <c r="N4" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>NOT OK</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>OK</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1424,12 +1629,18 @@
       <c r="F5" s="3" t="s">
         <v>229</v>
       </c>
+      <c r="H5" s="3" t="s">
+        <v>259</v>
+      </c>
       <c r="N5" s="7" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O5" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1450,10 +1661,13 @@
       </c>
       <c r="N6" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>NOT OK</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1474,10 +1688,13 @@
       </c>
       <c r="N7" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>NOT OK</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1487,12 +1704,36 @@
       <c r="C8" t="s">
         <v>11</v>
       </c>
+      <c r="D8" t="s">
+        <v>280</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>284</v>
+      </c>
       <c r="N8" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>NOT OK</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>OK</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1527,8 +1768,11 @@
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O9" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1557,8 +1801,11 @@
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O10" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -1568,12 +1815,19 @@
       <c r="C11" t="s">
         <v>11</v>
       </c>
+      <c r="E11" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>292</v>
+      </c>
       <c r="N11" s="7" t="str">
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O11" s="7"/>
+    </row>
+    <row r="12" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -1592,6 +1846,9 @@
       <c r="F12" s="3" t="s">
         <v>236</v>
       </c>
+      <c r="H12" s="3" t="s">
+        <v>267</v>
+      </c>
       <c r="J12" s="3" t="s">
         <v>211</v>
       </c>
@@ -1602,8 +1859,9 @@
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O12" s="7"/>
+    </row>
+    <row r="13" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -1622,15 +1880,21 @@
       <c r="F13" s="3" t="s">
         <v>237</v>
       </c>
+      <c r="G13" s="3" t="s">
+        <v>293</v>
+      </c>
       <c r="I13" s="3" t="s">
         <v>131</v>
       </c>
       <c r="N13" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>NOT OK</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -1649,6 +1913,9 @@
       <c r="F14" s="3" t="s">
         <v>228</v>
       </c>
+      <c r="H14" s="3" t="s">
+        <v>285</v>
+      </c>
       <c r="K14" s="3" t="s">
         <v>133</v>
       </c>
@@ -1656,8 +1923,11 @@
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O14" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -1671,8 +1941,11 @@
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O15" s="7" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>48</v>
       </c>
@@ -1686,8 +1959,11 @@
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O16" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -1713,8 +1989,11 @@
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O17" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>52</v>
       </c>
@@ -1728,8 +2007,9 @@
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O18" s="7"/>
+    </row>
+    <row r="19" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>53</v>
       </c>
@@ -1743,8 +2023,9 @@
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O19" s="7"/>
+    </row>
+    <row r="20" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -1764,8 +2045,9 @@
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O20" s="7"/>
+    </row>
+    <row r="21" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>56</v>
       </c>
@@ -1779,8 +2061,11 @@
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O21" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -1794,8 +2079,11 @@
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O22" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -1815,8 +2103,11 @@
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O23" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>62</v>
       </c>
@@ -1826,12 +2117,25 @@
       <c r="C24" t="s">
         <v>11</v>
       </c>
+      <c r="D24" t="s">
+        <v>294</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>264</v>
+      </c>
       <c r="N24" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>NOT OK</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>OK</v>
+      </c>
+      <c r="O24" s="7"/>
+    </row>
+    <row r="25" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>64</v>
       </c>
@@ -1847,12 +2151,19 @@
       <c r="E25" s="5" t="s">
         <v>216</v>
       </c>
+      <c r="F25" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>297</v>
+      </c>
       <c r="N25" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>NOT OK</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>OK</v>
+      </c>
+      <c r="O25" s="7"/>
+    </row>
+    <row r="26" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>66</v>
       </c>
@@ -1873,10 +2184,13 @@
       </c>
       <c r="N26" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>NOT OK</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>68</v>
       </c>
@@ -1908,8 +2222,11 @@
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O27" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>69</v>
       </c>
@@ -1928,12 +2245,21 @@
       <c r="F28" s="3" t="s">
         <v>231</v>
       </c>
+      <c r="G28" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>268</v>
+      </c>
       <c r="N28" s="7" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O28" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>72</v>
       </c>
@@ -1952,12 +2278,21 @@
       <c r="F29" s="3" t="s">
         <v>232</v>
       </c>
+      <c r="G29" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="N29" s="7" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O29" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>73</v>
       </c>
@@ -1976,18 +2311,24 @@
       <c r="F30" s="3" t="s">
         <v>239</v>
       </c>
+      <c r="H30" s="3" t="s">
+        <v>286</v>
+      </c>
       <c r="K30" s="3" t="s">
         <v>154</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="N30" s="8" t="str">
+      <c r="N30" s="7" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O30" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>76</v>
       </c>
@@ -1997,12 +2338,25 @@
       <c r="C31" t="s">
         <v>11</v>
       </c>
-      <c r="N31" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>NOT OK</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D31" t="s">
+        <v>301</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="N31" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="O31" s="7"/>
+    </row>
+    <row r="32" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>79</v>
       </c>
@@ -2021,12 +2375,15 @@
       <c r="F32" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="N32" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N32" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+      <c r="O32" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>22</v>
       </c>
@@ -2045,12 +2402,15 @@
       <c r="F33" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="N33" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N33" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+      <c r="O33" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>19</v>
       </c>
@@ -2060,12 +2420,13 @@
       <c r="C34" t="s">
         <v>20</v>
       </c>
-      <c r="N34" s="8" t="str">
+      <c r="N34" s="7" t="str">
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O34" s="7"/>
+    </row>
+    <row r="35" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>83</v>
       </c>
@@ -2093,12 +2454,15 @@
       <c r="K35" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="N35" s="8" t="str">
+      <c r="N35" s="7" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O35" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>84</v>
       </c>
@@ -2117,12 +2481,16 @@
       <c r="F36" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="N36" s="8" t="str">
+      <c r="H36" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="N36" s="7" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O36" s="7"/>
+    </row>
+    <row r="37" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -2132,12 +2500,13 @@
       <c r="C37" t="s">
         <v>20</v>
       </c>
-      <c r="N37" s="8" t="str">
+      <c r="N37" s="7" t="str">
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O37" s="7"/>
+    </row>
+    <row r="38" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -2165,12 +2534,15 @@
       <c r="K38" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="N38" s="8" t="str">
+      <c r="N38" s="7" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O38" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -2180,12 +2552,15 @@
       <c r="C39" t="s">
         <v>20</v>
       </c>
-      <c r="N39" s="8" t="str">
+      <c r="N39" s="7" t="str">
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O39" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>87</v>
       </c>
@@ -2195,12 +2570,13 @@
       <c r="C40" t="s">
         <v>20</v>
       </c>
-      <c r="N40" s="8" t="str">
+      <c r="N40" s="7" t="str">
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O40" s="7"/>
+    </row>
+    <row r="41" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>89</v>
       </c>
@@ -2213,12 +2589,15 @@
       <c r="E41" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="N41" s="8" t="str">
+      <c r="N41" s="7" t="str">
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O41" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>91</v>
       </c>
@@ -2237,12 +2616,18 @@
       <c r="F42" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="N42" s="8" t="str">
+      <c r="H42" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="N42" s="7" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O42" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>93</v>
       </c>
@@ -2255,15 +2640,21 @@
       <c r="E43" s="5" t="s">
         <v>181</v>
       </c>
+      <c r="H43" s="3" t="s">
+        <v>260</v>
+      </c>
       <c r="K43" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="N43" s="8" t="str">
+      <c r="N43" s="7" t="str">
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O43" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>94</v>
       </c>
@@ -2288,12 +2679,15 @@
       <c r="L44" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="N44" s="8" t="str">
+      <c r="N44" s="7" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O44" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>97</v>
       </c>
@@ -2312,12 +2706,18 @@
       <c r="F45" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="N45" s="8" t="str">
+      <c r="H45" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="N45" s="7" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O45" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>98</v>
       </c>
@@ -2339,12 +2739,15 @@
       <c r="J46" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="N46" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N46" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+      <c r="O46" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>100</v>
       </c>
@@ -2357,6 +2760,9 @@
       <c r="E47" s="5" t="s">
         <v>188</v>
       </c>
+      <c r="F47" s="3" t="s">
+        <v>303</v>
+      </c>
       <c r="H47" s="3" t="s">
         <v>191</v>
       </c>
@@ -2366,12 +2772,15 @@
       <c r="K47" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="N47" s="8" t="str">
+      <c r="N47" s="7" t="str">
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O47" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>23</v>
       </c>
@@ -2381,12 +2790,15 @@
       <c r="C48" t="s">
         <v>24</v>
       </c>
-      <c r="N48" s="8" t="str">
+      <c r="N48" s="7" t="str">
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O48" s="7" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>103</v>
       </c>
@@ -2396,12 +2808,31 @@
       <c r="C49" t="s">
         <v>24</v>
       </c>
-      <c r="N49" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>NOT OK</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D49" t="s">
+        <v>304</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="N49" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="O49" s="7"/>
+    </row>
+    <row r="50" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>105</v>
       </c>
@@ -2417,12 +2848,15 @@
       <c r="E50" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="N50" s="8" t="str">
+      <c r="N50" s="7" t="str">
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O50" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>108</v>
       </c>
@@ -2441,12 +2875,18 @@
       <c r="F51" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="N51" s="8" t="str">
+      <c r="H51" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="N51" s="7" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O51" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>109</v>
       </c>
@@ -2465,15 +2905,19 @@
       <c r="F52" s="3" t="s">
         <v>251</v>
       </c>
+      <c r="H52" s="3" t="s">
+        <v>263</v>
+      </c>
       <c r="K52" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="N52" s="8" t="str">
+      <c r="N52" s="7" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O52" s="7"/>
+    </row>
+    <row r="53" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>111</v>
       </c>
@@ -2492,12 +2936,18 @@
       <c r="F53" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="N53" s="8" t="str">
+      <c r="H53" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="N53" s="7" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O53" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>113</v>
       </c>
@@ -2516,12 +2966,18 @@
       <c r="F54" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="N54" s="8" t="str">
+      <c r="H54" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="N54" s="7" t="str">
         <f t="shared" si="0"/>
         <v>OK</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O54" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>115</v>
       </c>
@@ -2537,12 +2993,15 @@
       <c r="E55" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="N55" s="8" t="str">
+      <c r="N55" s="7" t="str">
         <f t="shared" si="0"/>
         <v>NOT OK</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O55" s="7" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>117</v>
       </c>
@@ -2561,12 +3020,15 @@
       <c r="F56" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="N56" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N56" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT OK</v>
+      </c>
+      <c r="O56" s="7" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>118</v>
       </c>
@@ -2576,13 +3038,32 @@
       <c r="C57" t="s">
         <v>107</v>
       </c>
-      <c r="N57" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>NOT OK</v>
-      </c>
+      <c r="D57" t="s">
+        <v>310</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="N57" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>OK</v>
+      </c>
+      <c r="O57" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N57" xr:uid="{CC0F6B4F-BD8C-3745-9181-6C92BF1467A2}"/>
+  <autoFilter ref="A1:O57" xr:uid="{CC0F6B4F-BD8C-3745-9181-6C92BF1467A2}"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
@@ -2654,8 +3135,51 @@
     <hyperlink ref="F17" r:id="rId60" xr:uid="{35940410-BC23-AC4B-A7AF-C89A745648CA}"/>
     <hyperlink ref="F54" r:id="rId61" xr:uid="{C4BEFDE5-6D1F-3842-A4ED-8CE7D5A429B1}"/>
     <hyperlink ref="F56" r:id="rId62" xr:uid="{061E23FF-74A9-484F-8DEC-0693638A5736}"/>
+    <hyperlink ref="H54" r:id="rId63" xr:uid="{6AD9161F-5E73-724A-980A-02B4F8D280FF}"/>
+    <hyperlink ref="H5" r:id="rId64" xr:uid="{973018E5-33CB-BE46-97C9-C055FFD184D9}"/>
+    <hyperlink ref="H43" r:id="rId65" xr:uid="{00A010B5-5F1B-B34C-B045-76CE5F2815F3}"/>
+    <hyperlink ref="H51" r:id="rId66" xr:uid="{40203D5F-FF04-3B46-8607-2296F5F4EA58}"/>
+    <hyperlink ref="H36" r:id="rId67" xr:uid="{E32C0D1B-37BC-F346-9A8F-89924E315A24}"/>
+    <hyperlink ref="H52" r:id="rId68" xr:uid="{868B9A50-4327-1B41-B520-64068A0EED2E}"/>
+    <hyperlink ref="H24" r:id="rId69" xr:uid="{4F0F18D9-85E5-EC41-90D0-E84DC639EE42}"/>
+    <hyperlink ref="H57" r:id="rId70" xr:uid="{E4B84F95-5F41-4B48-8AFB-E22327605768}"/>
+    <hyperlink ref="H3" r:id="rId71" xr:uid="{53BCCF90-9AFE-DD44-A519-63827A7540A6}"/>
+    <hyperlink ref="H12" r:id="rId72" xr:uid="{E2FA523E-A86D-C148-A9EE-EEA60AD73A15}"/>
+    <hyperlink ref="H28" r:id="rId73" xr:uid="{BC1AB687-50AD-D148-95D6-BDCF52EFAF50}"/>
+    <hyperlink ref="H29" r:id="rId74" xr:uid="{336FBA4E-5D3E-A747-A6B2-90856807A694}"/>
+    <hyperlink ref="H45" r:id="rId75" xr:uid="{2D170E62-C156-174F-ADBA-B488D0E63A08}"/>
+    <hyperlink ref="H42" r:id="rId76" xr:uid="{778D4A73-7600-694E-BE25-6DD9BFC6088E}"/>
+    <hyperlink ref="G28" r:id="rId77" xr:uid="{9929021F-1265-3B48-A3AD-E26CD7873621}"/>
+    <hyperlink ref="G29" r:id="rId78" xr:uid="{BB34559A-D137-994A-AB14-E8C7C454992C}"/>
+    <hyperlink ref="H2" r:id="rId79" xr:uid="{D37AF6B8-EB6F-C74D-9405-77A898859086}"/>
+    <hyperlink ref="H8" r:id="rId80" xr:uid="{0E4B4BEA-CDF9-9445-A586-AD42626E8CC2}"/>
+    <hyperlink ref="F8" r:id="rId81" xr:uid="{3537D541-AE69-694A-BBF2-DBF06607EDFB}"/>
+    <hyperlink ref="K8" r:id="rId82" xr:uid="{31FAC43A-41C9-B14A-BAA7-615AD1F15080}"/>
+    <hyperlink ref="J8" r:id="rId83" xr:uid="{6D03E29C-C681-3142-B274-1CB0A0F43DD9}"/>
+    <hyperlink ref="L8" r:id="rId84" xr:uid="{711B93B5-8F28-2D45-8676-F6E36D385DF9}"/>
+    <hyperlink ref="H14" r:id="rId85" xr:uid="{6C8ABA91-06B6-1945-B640-44B33DC88653}"/>
+    <hyperlink ref="H30" r:id="rId86" xr:uid="{01588519-65D8-374F-8442-74570C1DB917}"/>
+    <hyperlink ref="F4" r:id="rId87" xr:uid="{4A4633D4-A102-3E42-8AD6-1E1AF590F3DC}"/>
+    <hyperlink ref="H4" r:id="rId88" xr:uid="{29CD960C-44F3-6B43-A2BA-2EF7F53DACB5}"/>
+    <hyperlink ref="F11" r:id="rId89" xr:uid="{81905E60-0CF4-BC48-973E-969DA6BE02E3}"/>
+    <hyperlink ref="G13" r:id="rId90" xr:uid="{3C44ABF8-A1A1-DF4B-A8E8-6C43A9EA9D05}"/>
+    <hyperlink ref="F24" r:id="rId91" xr:uid="{26DECFD7-49EA-964E-90AF-7A29EDF5FF48}"/>
+    <hyperlink ref="H25" r:id="rId92" xr:uid="{3210B8E9-8164-7C4A-8224-1EA59D450A2D}"/>
+    <hyperlink ref="F25" r:id="rId93" xr:uid="{F8E86FC8-983E-0646-9B7C-1A3D0E0F9F47}"/>
+    <hyperlink ref="H31" r:id="rId94" xr:uid="{206255CA-B45D-FA43-9A24-14A19483952F}"/>
+    <hyperlink ref="F31" r:id="rId95" xr:uid="{0C20FAF0-214C-F84F-B06B-C7A9CEFE60AC}"/>
+    <hyperlink ref="F47" r:id="rId96" xr:uid="{277133BE-6F88-9140-A9F5-FD3BB3C73583}"/>
+    <hyperlink ref="F49" r:id="rId97" xr:uid="{9F673F72-4F06-1A46-B46C-4FD4041220D9}"/>
+    <hyperlink ref="H49" r:id="rId98" xr:uid="{C2E83D72-9C10-1641-A7FA-558DA23A213C}"/>
+    <hyperlink ref="J49" r:id="rId99" xr:uid="{0FE40355-122D-2C4C-9420-CEB362AECDC4}"/>
+    <hyperlink ref="K49" r:id="rId100" xr:uid="{83B59012-8B12-6D41-B18E-FB997563C33F}"/>
+    <hyperlink ref="H53" r:id="rId101" xr:uid="{D466EA00-24CD-594A-B571-38BE8D22BB15}"/>
+    <hyperlink ref="F57" r:id="rId102" xr:uid="{97125438-9D22-E641-93B7-877040CA22F2}"/>
+    <hyperlink ref="G57" r:id="rId103" xr:uid="{40B0A75B-8C0E-864A-A7D3-BCFE5B62F00D}"/>
+    <hyperlink ref="J57" r:id="rId104" xr:uid="{3889E866-8B99-CB4B-A4FF-415C36A9B23A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
